--- a/VOYAGES/2026-10-20_KTS1_KJT_2611N_THBKK_BKK01/2026-10-20_KTS1_KJT_2611N_THBKK_BKK01.xlsx
+++ b/VOYAGES/2026-10-20_KTS1_KJT_2611N_THBKK_BKK01/2026-10-20_KTS1_KJT_2611N_THBKK_BKK01.xlsx
@@ -1034,7 +1034,7 @@
     <row r="27">
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>คำนวณเมื่อ: 20/10/2026 18:04</t>
+          <t>คำนวณเมื่อ: 20/10/2026 18:13</t>
         </is>
       </c>
     </row>
